--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
   <si>
     <t>FLEX</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>30346000</v>
+        <v>26415000</v>
       </c>
       <c r="E8" s="3">
-        <v>26041000</v>
+        <v>28502000</v>
       </c>
       <c r="F8" s="3">
+        <v>24633000</v>
+      </c>
+      <c r="G8" s="3">
         <v>24124000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24210000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>26211000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>25441100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23862900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24418900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>26147900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26108600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>23569500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>29343000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>28058000</v>
+        <v>24395000</v>
       </c>
       <c r="E9" s="3">
-        <v>24094000</v>
+        <v>26503000</v>
       </c>
       <c r="F9" s="3">
+        <v>22838000</v>
+      </c>
+      <c r="G9" s="3">
         <v>22349000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22681000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>24594000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23778400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22303200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22810800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>24602600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24609700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>44374800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>27825100</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2288000</v>
+        <v>2020000</v>
       </c>
       <c r="E10" s="3">
-        <v>1947000</v>
+        <v>1999000</v>
       </c>
       <c r="F10" s="3">
+        <v>1795000</v>
+      </c>
+      <c r="G10" s="3">
         <v>1775000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1529000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1617000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1662700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1559700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1608100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1545300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1498900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-20805300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1518000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E14" s="3">
         <v>27000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-133000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>138000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>321200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>233300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>90700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>49400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>75300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>227400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-20000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>82000</v>
+        <v>70000</v>
       </c>
       <c r="E15" s="3">
-        <v>68000</v>
+        <v>81000</v>
       </c>
       <c r="F15" s="3">
+        <v>60000</v>
+      </c>
+      <c r="G15" s="3">
         <v>62000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>64000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>74000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>78600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>81400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>66000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>32000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>28900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>29500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>49600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>29162000</v>
+        <v>25562000</v>
       </c>
       <c r="E17" s="3">
-        <v>24844000</v>
+        <v>27485000</v>
       </c>
       <c r="F17" s="3">
+        <v>23743000</v>
+      </c>
+      <c r="G17" s="3">
         <v>23262000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23884200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>25854000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24797400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23392600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23871400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25425900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25646200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23184400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28768300</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1184000</v>
+        <v>853000</v>
       </c>
       <c r="E18" s="3">
-        <v>1197000</v>
+        <v>1017000</v>
       </c>
       <c r="F18" s="3">
+        <v>890000</v>
+      </c>
+      <c r="G18" s="3">
         <v>862000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>325800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>357000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>643700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>470400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>547500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>722100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>462400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>385100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>574700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-23000</v>
+        <v>20000</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="F20" s="3">
+        <v>240000</v>
+      </c>
+      <c r="G20" s="3">
         <v>2000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-28000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>5200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>18000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12600</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1662000</v>
+        <v>1410000</v>
       </c>
       <c r="E21" s="3">
-        <v>1682000</v>
+        <v>1538000</v>
       </c>
       <c r="F21" s="3">
+        <v>1614000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1433000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1045900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1093000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1199400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1088500</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>944900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>964100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1096700</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>187000</v>
+        <v>207000</v>
       </c>
       <c r="E22" s="3">
-        <v>153000</v>
+        <v>230000</v>
       </c>
       <c r="F22" s="3">
+        <v>166000</v>
+      </c>
+      <c r="G22" s="3">
         <v>150000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>138800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>146000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>123100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>108000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>98000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>76400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>79900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>68900</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>974000</v>
+        <v>666000</v>
       </c>
       <c r="E23" s="3">
-        <v>1045000</v>
+        <v>807000</v>
       </c>
       <c r="F23" s="3">
+        <v>964000</v>
+      </c>
+      <c r="G23" s="3">
         <v>714000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>159000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>182000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>520900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>370800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>454700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>670700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>328800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>574700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-59000</v>
+        <v>-206000</v>
       </c>
       <c r="E24" s="3">
-        <v>105000</v>
+        <v>124000</v>
       </c>
       <c r="F24" s="3">
+        <v>92000</v>
+      </c>
+      <c r="G24" s="3">
         <v>101000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>71000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>89000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>92400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>51300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>10600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>69900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>34900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>54000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1033000</v>
+        <v>872000</v>
       </c>
       <c r="E26" s="3">
-        <v>940000</v>
+        <v>683000</v>
       </c>
       <c r="F26" s="3">
+        <v>872000</v>
+      </c>
+      <c r="G26" s="3">
         <v>613000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>88000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>93000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>428500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>319600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>444100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>600800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>365600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>302500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>520800</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>793000</v>
+        <v>872000</v>
       </c>
       <c r="E27" s="3">
-        <v>936000</v>
+        <v>443000</v>
       </c>
       <c r="F27" s="3">
+        <v>868000</v>
+      </c>
+      <c r="G27" s="3">
         <v>613000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>88000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>93000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>428500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>319600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>444100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>600800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>365600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>302500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>520800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,32 +1582,35 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>134000</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>64000</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1562,14 +1622,17 @@
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-25500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-32000</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>23000</v>
+        <v>-20000</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="F32" s="3">
+        <v>-240000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>28000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-5200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-18000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12600</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>793000</v>
+        <v>1006000</v>
       </c>
       <c r="E33" s="3">
-        <v>936000</v>
+        <v>553000</v>
       </c>
       <c r="F33" s="3">
+        <v>932000</v>
+      </c>
+      <c r="G33" s="3">
         <v>613000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>88000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>93000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>428500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>319600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>444100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>600800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>365600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>277100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>488800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>793000</v>
+        <v>1006000</v>
       </c>
       <c r="E35" s="3">
-        <v>936000</v>
+        <v>553000</v>
       </c>
       <c r="F35" s="3">
+        <v>932000</v>
+      </c>
+      <c r="G35" s="3">
         <v>613000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>88000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>93000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>428500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>319600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>444100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>600800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>365600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>277100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>488800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,50 +1988,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3294000</v>
+        <v>2474000</v>
       </c>
       <c r="E41" s="3">
+        <v>3164000</v>
+      </c>
+      <c r="F41" s="3">
         <v>2964000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2637000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1922700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1696600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1472400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1830700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1607600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1628400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1593700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1587100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1174400</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,199 +2073,214 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>343900</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4280000</v>
+        <v>3282000</v>
       </c>
       <c r="E43" s="3">
+        <v>3723000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3890000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4241000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2718400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2829200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2517700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2192700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2044800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2337500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2698000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2112000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2593800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7530000</v>
+        <v>6205000</v>
       </c>
       <c r="E44" s="3">
+        <v>7388000</v>
+      </c>
+      <c r="F44" s="3">
         <v>6580000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3895000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3785100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3722900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3799800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3396500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3491700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3488800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3599000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2722500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3300800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>917000</v>
+        <v>1031000</v>
       </c>
       <c r="E45" s="3">
+        <v>1758000</v>
+      </c>
+      <c r="F45" s="3">
         <v>903000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>590000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>660100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>854800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1380500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>967900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1171100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1286200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1509600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1349800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1121600</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>16021000</v>
+        <v>12992000</v>
       </c>
       <c r="E46" s="3">
+        <v>16033000</v>
+      </c>
+      <c r="F46" s="3">
         <v>14337000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11363000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9086300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9103400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9170400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8387800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8315100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8740900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9400300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7771400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8534500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>115000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>131300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>102800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>128100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>294100</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -2193,96 +2297,105 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2957000</v>
+        <v>2870000</v>
       </c>
       <c r="E48" s="3">
+        <v>2947000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2762000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2739000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2821100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2336200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2239500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2317000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2257600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2092200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2288700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2174600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2076400</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1659000</v>
+        <v>1380000</v>
       </c>
       <c r="E49" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1753000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1303000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1327000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1404000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1545600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1347000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1345800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>415200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>377200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>343600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>31400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>643000</v>
+        <v>1015000</v>
       </c>
       <c r="E52" s="3">
+        <v>1616000</v>
+      </c>
+      <c r="F52" s="3">
         <v>341700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>328200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>327200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>361600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>760300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>541500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>466400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>404600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>433900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>302000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>262900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21395000</v>
+        <v>18257000</v>
       </c>
       <c r="E54" s="3">
+        <v>21407000</v>
+      </c>
+      <c r="F54" s="3">
         <v>19325000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15836000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13689600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13499400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13715900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12593400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12385000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11652900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12500100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10591600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11033800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5930000</v>
+        <v>4468000</v>
       </c>
       <c r="E57" s="3">
+        <v>5724000</v>
+      </c>
+      <c r="F57" s="3">
         <v>6254000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5247000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5108300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5147200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5122300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4484900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4248300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4561200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4747800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3705300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4294900</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>150000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>949000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>268000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>149100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>632600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>43000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>61500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>65200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>45000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>419500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42400</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4775000</v>
+        <v>4071000</v>
       </c>
       <c r="E59" s="3">
+        <v>4993000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3508000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2319000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1953700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1817700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2102800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1958200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2258700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3958000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2872100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2048000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1950900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10855000</v>
+        <v>8539000</v>
       </c>
       <c r="E60" s="3">
+        <v>10867000</v>
+      </c>
+      <c r="F60" s="3">
         <v>10711000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7834000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7211100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7597500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7268100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6504600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6572200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6755100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7656700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6172800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6288200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3691000</v>
+        <v>3261000</v>
       </c>
       <c r="E61" s="3">
+        <v>3544000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3248000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3515000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2689100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2421900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2897600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2890600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2709400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2026000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2074700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1657300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2157800</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1143000</v>
+        <v>1132000</v>
       </c>
       <c r="E62" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="F62" s="3">
         <v>1159000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1051000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>958300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>507600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>531600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>519900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>497900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>475600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>567100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>514700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>607600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16044000</v>
+        <v>12932000</v>
       </c>
       <c r="E66" s="3">
+        <v>16056000</v>
+      </c>
+      <c r="F66" s="3">
         <v>15196000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12400000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10858500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10527000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10697300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9948800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9814100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9292100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10337100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8344800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8749800</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3090,9 +3257,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-560000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1353000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2289000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2902400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3012000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3144100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3572600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3892200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-4336300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4937100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-5302700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5579700</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5325000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5351000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4129000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3436000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2831200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2972400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3018600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2644500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2570900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2360800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2163100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2246800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2284000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>793000</v>
+        <v>1006000</v>
       </c>
       <c r="E81" s="3">
-        <v>936000</v>
+        <v>553000</v>
       </c>
       <c r="F81" s="3">
+        <v>932000</v>
+      </c>
+      <c r="G81" s="3">
         <v>613000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>88000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>93000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>428500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>319600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>444100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>600800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>365600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>277100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>488800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>537000</v>
+      </c>
+      <c r="E83" s="3">
         <v>501000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>484000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>569000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>748100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>765000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>555400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>609700</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>464500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>566400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>521900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1326000</v>
+      </c>
+      <c r="E89" s="3">
         <v>950000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1024000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>144000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1533300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2971000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3866300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3822100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>794000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>1216500</v>
       </c>
       <c r="M89" s="3">
         <v>1216500</v>
       </c>
       <c r="N89" s="3">
+        <v>1216500</v>
+      </c>
+      <c r="O89" s="3">
         <v>1115400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>804300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-530000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-635000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-443000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-351000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-461700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-725600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-562000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-525100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-347400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-609600</v>
       </c>
       <c r="M91" s="3">
         <v>-609600</v>
       </c>
       <c r="N91" s="3">
+        <v>-609600</v>
+      </c>
+      <c r="O91" s="3">
         <v>-489000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-437200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-492000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-604000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-951000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-202000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2279000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>3252900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3710900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>4269800</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N94" s="3">
         <v>-783900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-697200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-481400</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,8 +4222,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4031,9 +4264,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1656000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>280000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>743000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-508500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-187800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-242100</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N100" s="3">
         <v>-410800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-339600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-522200</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-26000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>29000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-28000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-15100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>17500</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3">
         <v>-15100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-30900</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-820000</v>
+      </c>
+      <c r="E102" s="3">
         <v>330000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>327000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>714000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>226100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>224200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-358300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>223100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34700</v>
-      </c>
-      <c r="L102" s="3">
-        <v>6600</v>
       </c>
       <c r="M102" s="3">
         <v>6600</v>
       </c>
       <c r="N102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="O102" s="3">
         <v>68800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-230100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>FLEX</t>
   </si>
@@ -2264,8 +2264,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>123000</v>
       </c>
       <c r="E47" s="3">
         <v>115000</v>
@@ -2490,7 +2490,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1015000</v>
+        <v>892000</v>
       </c>
       <c r="E52" s="3">
         <v>1616000</v>

--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>FLEX</t>
   </si>
@@ -978,7 +978,7 @@
         <v>27000</v>
       </c>
       <c r="F14" s="3">
-        <v>-133000</v>
+        <v>15000</v>
       </c>
       <c r="G14" s="3">
         <v>138000</v>
@@ -987,10 +987,10 @@
         <v>321200</v>
       </c>
       <c r="I14" s="3">
-        <v>233300</v>
+        <v>219000</v>
       </c>
       <c r="J14" s="3">
-        <v>90700</v>
+        <v>-77700</v>
       </c>
       <c r="K14" s="3">
         <v>49400</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>25562000</v>
+        <v>25387000</v>
       </c>
       <c r="E17" s="3">
-        <v>27485000</v>
+        <v>27458000</v>
       </c>
       <c r="F17" s="3">
-        <v>23743000</v>
+        <v>23728000</v>
       </c>
       <c r="G17" s="3">
-        <v>23262000</v>
+        <v>23228000</v>
       </c>
       <c r="H17" s="3">
-        <v>23884200</v>
+        <v>23579000</v>
       </c>
       <c r="I17" s="3">
-        <v>25854000</v>
+        <v>25621000</v>
       </c>
       <c r="J17" s="3">
-        <v>24797400</v>
+        <v>24876400</v>
       </c>
       <c r="K17" s="3">
         <v>23392600</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>853000</v>
+        <v>1028000</v>
       </c>
       <c r="E18" s="3">
-        <v>1017000</v>
+        <v>1044000</v>
       </c>
       <c r="F18" s="3">
-        <v>890000</v>
+        <v>905000</v>
       </c>
       <c r="G18" s="3">
-        <v>862000</v>
+        <v>896000</v>
       </c>
       <c r="H18" s="3">
-        <v>325800</v>
+        <v>631000</v>
       </c>
       <c r="I18" s="3">
-        <v>357000</v>
+        <v>590000</v>
       </c>
       <c r="J18" s="3">
-        <v>643700</v>
+        <v>564700</v>
       </c>
       <c r="K18" s="3">
         <v>470400</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>20000</v>
+        <v>36000</v>
       </c>
       <c r="E20" s="3">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="3">
-        <v>240000</v>
+        <v>-226000</v>
       </c>
       <c r="G20" s="3">
-        <v>2000</v>
+        <v>-104000</v>
       </c>
       <c r="H20" s="3">
-        <v>-28000</v>
+        <v>31000</v>
       </c>
       <c r="I20" s="3">
-        <v>-29000</v>
+        <v>62000</v>
       </c>
       <c r="J20" s="3">
-        <v>300</v>
+        <v>17200</v>
       </c>
       <c r="K20" s="3">
         <v>8500</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1410000</v>
+        <v>1062000</v>
       </c>
       <c r="E21" s="3">
-        <v>1538000</v>
+        <v>1115000</v>
       </c>
       <c r="F21" s="3">
-        <v>1614000</v>
+        <v>1191000</v>
       </c>
       <c r="G21" s="3">
-        <v>1433000</v>
+        <v>1062000</v>
       </c>
       <c r="H21" s="3">
-        <v>1045900</v>
+        <v>664000</v>
       </c>
       <c r="I21" s="3">
-        <v>1093000</v>
+        <v>602000</v>
       </c>
       <c r="J21" s="3">
-        <v>1199400</v>
+        <v>626100</v>
       </c>
       <c r="K21" s="3">
         <v>1088500</v>
@@ -1286,7 +1286,7 @@
         <v>166000</v>
       </c>
       <c r="G22" s="3">
-        <v>150000</v>
+        <v>162000</v>
       </c>
       <c r="H22" s="3">
         <v>138800</v>
@@ -1502,13 +1502,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>872000</v>
+        <v>1006000</v>
       </c>
       <c r="E27" s="3">
-        <v>443000</v>
+        <v>793000</v>
       </c>
       <c r="F27" s="3">
-        <v>868000</v>
+        <v>936000</v>
       </c>
       <c r="G27" s="3">
         <v>613000</v>
@@ -1592,25 +1592,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>134000</v>
+        <v>373000</v>
       </c>
       <c r="E29" s="3">
-        <v>110000</v>
+        <v>350000</v>
       </c>
       <c r="F29" s="3">
-        <v>64000</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>68000</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-20000</v>
+        <v>-36000</v>
       </c>
       <c r="E32" s="3">
-        <v>-20000</v>
+        <v>-10000</v>
       </c>
       <c r="F32" s="3">
-        <v>-240000</v>
+        <v>226000</v>
       </c>
       <c r="G32" s="3">
-        <v>-2000</v>
+        <v>104000</v>
       </c>
       <c r="H32" s="3">
-        <v>28000</v>
+        <v>-31000</v>
       </c>
       <c r="I32" s="3">
-        <v>29000</v>
+        <v>-62000</v>
       </c>
       <c r="J32" s="3">
-        <v>-300</v>
+        <v>-17200</v>
       </c>
       <c r="K32" s="3">
         <v>-8500</v>
@@ -1775,10 +1775,10 @@
         <v>1006000</v>
       </c>
       <c r="E33" s="3">
-        <v>553000</v>
+        <v>793000</v>
       </c>
       <c r="F33" s="3">
-        <v>932000</v>
+        <v>936000</v>
       </c>
       <c r="G33" s="3">
         <v>613000</v>
@@ -1865,10 +1865,10 @@
         <v>1006000</v>
       </c>
       <c r="E35" s="3">
-        <v>553000</v>
+        <v>793000</v>
       </c>
       <c r="F35" s="3">
-        <v>932000</v>
+        <v>936000</v>
       </c>
       <c r="G35" s="3">
         <v>613000</v>
@@ -2007,7 +2007,7 @@
         <v>2637000</v>
       </c>
       <c r="H41" s="3">
-        <v>1922700</v>
+        <v>1923000</v>
       </c>
       <c r="I41" s="3">
         <v>1696600</v>
@@ -2097,13 +2097,13 @@
         <v>4241000</v>
       </c>
       <c r="H43" s="3">
-        <v>2718400</v>
+        <v>2718000</v>
       </c>
       <c r="I43" s="3">
-        <v>2829200</v>
+        <v>3121700</v>
       </c>
       <c r="J43" s="3">
-        <v>2517700</v>
+        <v>2963100</v>
       </c>
       <c r="K43" s="3">
         <v>2192700</v>
@@ -2142,7 +2142,7 @@
         <v>3895000</v>
       </c>
       <c r="H44" s="3">
-        <v>3785100</v>
+        <v>3785000</v>
       </c>
       <c r="I44" s="3">
         <v>3722900</v>
@@ -2187,13 +2187,13 @@
         <v>590000</v>
       </c>
       <c r="H45" s="3">
-        <v>660100</v>
+        <v>660000</v>
       </c>
       <c r="I45" s="3">
-        <v>854800</v>
+        <v>562300</v>
       </c>
       <c r="J45" s="3">
-        <v>1380500</v>
+        <v>935100</v>
       </c>
       <c r="K45" s="3">
         <v>967900</v>
@@ -2232,7 +2232,7 @@
         <v>11363000</v>
       </c>
       <c r="H46" s="3">
-        <v>9086300</v>
+        <v>9086000</v>
       </c>
       <c r="I46" s="3">
         <v>9103400</v>
@@ -2271,7 +2271,7 @@
         <v>115000</v>
       </c>
       <c r="F47" s="3">
-        <v>131300</v>
+        <v>131000</v>
       </c>
       <c r="G47" s="3">
         <v>102800</v>
@@ -2280,10 +2280,10 @@
         <v>128100</v>
       </c>
       <c r="I47" s="3">
-        <v>294100</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
+        <v>421700</v>
+      </c>
+      <c r="J47" s="3">
+        <v>536100</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -2322,7 +2322,7 @@
         <v>2739000</v>
       </c>
       <c r="H48" s="3">
-        <v>2821100</v>
+        <v>2821000</v>
       </c>
       <c r="I48" s="3">
         <v>2336200</v>
@@ -2370,7 +2370,7 @@
         <v>1327000</v>
       </c>
       <c r="I49" s="3">
-        <v>1404000</v>
+        <v>1404100</v>
       </c>
       <c r="J49" s="3">
         <v>1545600</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>892000</v>
+        <v>248000</v>
       </c>
       <c r="E52" s="3">
-        <v>1616000</v>
+        <v>694000</v>
       </c>
       <c r="F52" s="3">
-        <v>341700</v>
+        <v>165000</v>
       </c>
       <c r="G52" s="3">
-        <v>328200</v>
+        <v>163200</v>
       </c>
       <c r="H52" s="3">
-        <v>327200</v>
+        <v>164900</v>
       </c>
       <c r="I52" s="3">
-        <v>361600</v>
+        <v>69300</v>
       </c>
       <c r="J52" s="3">
-        <v>760300</v>
+        <v>58900</v>
       </c>
       <c r="K52" s="3">
         <v>541500</v>
@@ -2592,7 +2592,7 @@
         <v>15836000</v>
       </c>
       <c r="H54" s="3">
-        <v>13689600</v>
+        <v>13690000</v>
       </c>
       <c r="I54" s="3">
         <v>13499400</v>
@@ -2675,7 +2675,7 @@
         <v>5247000</v>
       </c>
       <c r="H57" s="3">
-        <v>5108300</v>
+        <v>5108000</v>
       </c>
       <c r="I57" s="3">
         <v>5147200</v>
@@ -2708,19 +2708,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>137000</v>
       </c>
       <c r="E58" s="3">
-        <v>150000</v>
+        <v>274000</v>
       </c>
       <c r="F58" s="3">
-        <v>949000</v>
+        <v>1081000</v>
       </c>
       <c r="G58" s="3">
-        <v>268000</v>
+        <v>395600</v>
       </c>
       <c r="H58" s="3">
-        <v>149100</v>
+        <v>263100</v>
       </c>
       <c r="I58" s="3">
         <v>632600</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4071000</v>
+        <v>3446000</v>
       </c>
       <c r="E59" s="3">
-        <v>4993000</v>
+        <v>4363000</v>
       </c>
       <c r="F59" s="3">
-        <v>3508000</v>
+        <v>2906000</v>
       </c>
       <c r="G59" s="3">
-        <v>2319000</v>
+        <v>1718400</v>
       </c>
       <c r="H59" s="3">
-        <v>1953700</v>
+        <v>1475900</v>
       </c>
       <c r="I59" s="3">
-        <v>1817700</v>
+        <v>1426100</v>
       </c>
       <c r="J59" s="3">
-        <v>2102800</v>
+        <v>1719400</v>
       </c>
       <c r="K59" s="3">
         <v>1958200</v>
@@ -2810,7 +2810,7 @@
         <v>7834000</v>
       </c>
       <c r="H60" s="3">
-        <v>7211100</v>
+        <v>7211000</v>
       </c>
       <c r="I60" s="3">
         <v>7597500</v>
@@ -2843,19 +2843,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3261000</v>
+        <v>3751000</v>
       </c>
       <c r="E61" s="3">
-        <v>3544000</v>
+        <v>4048000</v>
       </c>
       <c r="F61" s="3">
-        <v>3248000</v>
+        <v>3799000</v>
       </c>
       <c r="G61" s="3">
-        <v>3515000</v>
+        <v>4077000</v>
       </c>
       <c r="H61" s="3">
-        <v>2689100</v>
+        <v>3218000</v>
       </c>
       <c r="I61" s="3">
         <v>2421900</v>
@@ -2888,19 +2888,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1132000</v>
+        <v>464000</v>
       </c>
       <c r="E62" s="3">
-        <v>1058000</v>
+        <v>715000</v>
       </c>
       <c r="F62" s="3">
-        <v>1159000</v>
+        <v>522000</v>
       </c>
       <c r="G62" s="3">
-        <v>1051000</v>
+        <v>489000</v>
       </c>
       <c r="H62" s="3">
-        <v>958300</v>
+        <v>430000</v>
       </c>
       <c r="I62" s="3">
         <v>507600</v>
@@ -3071,16 +3071,16 @@
         <v>12932000</v>
       </c>
       <c r="E66" s="3">
-        <v>16056000</v>
+        <v>15701000</v>
       </c>
       <c r="F66" s="3">
-        <v>15196000</v>
+        <v>15118000</v>
       </c>
       <c r="G66" s="3">
         <v>12400000</v>
       </c>
       <c r="H66" s="3">
-        <v>10858500</v>
+        <v>10859000</v>
       </c>
       <c r="I66" s="3">
         <v>10527000</v>
@@ -3324,7 +3324,7 @@
         <v>-2289000</v>
       </c>
       <c r="H72" s="3">
-        <v>-2902400</v>
+        <v>-2902000</v>
       </c>
       <c r="I72" s="3">
         <v>-3012000</v>
@@ -3504,7 +3504,7 @@
         <v>3436000</v>
       </c>
       <c r="H76" s="3">
-        <v>2831200</v>
+        <v>2831000</v>
       </c>
       <c r="I76" s="3">
         <v>2972400</v>
@@ -3635,10 +3635,10 @@
         <v>1006000</v>
       </c>
       <c r="E81" s="3">
-        <v>553000</v>
+        <v>793000</v>
       </c>
       <c r="F81" s="3">
-        <v>932000</v>
+        <v>936000</v>
       </c>
       <c r="G81" s="3">
         <v>613000</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>537000</v>
+        <v>431000</v>
       </c>
       <c r="E83" s="3">
-        <v>501000</v>
+        <v>414000</v>
       </c>
       <c r="F83" s="3">
-        <v>484000</v>
+        <v>409000</v>
       </c>
       <c r="G83" s="3">
-        <v>569000</v>
+        <v>422000</v>
       </c>
       <c r="H83" s="3">
-        <v>748100</v>
+        <v>422000</v>
       </c>
       <c r="I83" s="3">
-        <v>765000</v>
+        <v>433000</v>
       </c>
       <c r="J83" s="3">
-        <v>555400</v>
+        <v>434400</v>
       </c>
       <c r="K83" s="3">
         <v>609700</v>
@@ -3978,7 +3978,7 @@
         <v>144000</v>
       </c>
       <c r="H89" s="3">
-        <v>-1533300</v>
+        <v>-1533000</v>
       </c>
       <c r="I89" s="3">
         <v>-2971000</v>
@@ -4042,10 +4042,10 @@
         <v>-351000</v>
       </c>
       <c r="H91" s="3">
-        <v>-461700</v>
+        <v>-462000</v>
       </c>
       <c r="I91" s="3">
-        <v>-725600</v>
+        <v>-726000</v>
       </c>
       <c r="J91" s="3">
         <v>-562000</v>
@@ -4180,7 +4180,7 @@
         <v>2279000</v>
       </c>
       <c r="I94" s="3">
-        <v>3252900</v>
+        <v>3253000</v>
       </c>
       <c r="J94" s="3">
         <v>3710900</v>
@@ -4421,10 +4421,10 @@
         <v>743000</v>
       </c>
       <c r="H100" s="3">
-        <v>-508500</v>
+        <v>-508000</v>
       </c>
       <c r="I100" s="3">
-        <v>-29700</v>
+        <v>-30000</v>
       </c>
       <c r="J100" s="3">
         <v>-187800</v>
@@ -4466,10 +4466,10 @@
         <v>29000</v>
       </c>
       <c r="H101" s="3">
-        <v>-11200</v>
+        <v>-12000</v>
       </c>
       <c r="I101" s="3">
-        <v>-28000</v>
+        <v>-27000</v>
       </c>
       <c r="J101" s="3">
         <v>-15100</v>
@@ -4511,10 +4511,10 @@
         <v>714000</v>
       </c>
       <c r="H102" s="3">
-        <v>226100</v>
+        <v>226000</v>
       </c>
       <c r="I102" s="3">
-        <v>224200</v>
+        <v>225000</v>
       </c>
       <c r="J102" s="3">
         <v>-358300</v>

--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>FLEX</t>
   </si>
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25813000</v>
+      </c>
+      <c r="E8" s="3">
         <v>26415000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28502000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24633000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24124000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24210000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26211000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>25441100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23862900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24418900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26147900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26108600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>23569500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>29343000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>23584000</v>
+      </c>
+      <c r="E9" s="3">
         <v>24395000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26503000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>22838000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22349000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22681000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24594000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23778400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22303200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22810800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>24602600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24609700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>44374800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>27825100</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2229000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2020000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1999000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1795000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1775000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1529000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1617000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1662700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1559700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1608100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1545300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1498900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-20805300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1518000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,54 +981,60 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>86000</v>
+      </c>
+      <c r="E14" s="3">
         <v>175000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>27000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>138000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>321200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>219000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-77700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>49400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-8000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>75300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>227400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1020,44 +1042,47 @@
         <v>70000</v>
       </c>
       <c r="E15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="F15" s="3">
         <v>81000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>62000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>64000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>74000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>78600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>81400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>32000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>28900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>29500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>49600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24558000</v>
+      </c>
+      <c r="E17" s="3">
         <v>25387000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>27458000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>23728000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23228000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23579000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>25621000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24876400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23392600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23871400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25425900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25646200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23184400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>28768300</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1255000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1028000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1044000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>905000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>896000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>631000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>590000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>564700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>470400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>547500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>722100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>462400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>385100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>574700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>36000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-226000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-104000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>31000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>62000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>17200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>18000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12600</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1336000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1062000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1115000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1191000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1062000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>664000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>602000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>626100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1088500</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>944900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>964100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1096700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>218000</v>
+      </c>
+      <c r="E22" s="3">
         <v>207000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>230000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>166000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>162000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>138800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>146000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>123100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>108000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>98000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>76400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>79900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>68900</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1023000</v>
+      </c>
+      <c r="E23" s="3">
         <v>666000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>807000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>964000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>714000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>159000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>182000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>520900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>370800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>454700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>670700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>328800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>574700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>185000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-206000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>124000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>92000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>101000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>71000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>89000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>92400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>51300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>10600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>69900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>34900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>54000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E26" s="3">
         <v>872000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>683000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>872000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>613000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>88000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>93000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>428500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>319600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>444100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>600800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>365600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>302500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>520800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1006000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>793000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>936000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>613000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>88000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>93000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>428500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>319600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>444100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>600800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>365600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>302500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>520800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,24 +1642,27 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>373000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>350000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>68000</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1625,14 +1685,17 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-25500</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-36000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>226000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>104000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-31000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-62000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-17200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-18000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12600</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1006000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>793000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>936000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>613000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>88000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>93000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>428500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>319600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>444100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>600800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>365600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>277100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>488800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1006000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>793000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>936000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>613000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>88000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>93000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>428500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>319600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>444100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>600800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>365600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>277100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>488800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,53 +2074,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2289000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2474000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3164000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2964000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2637000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1923000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1696600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1472400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1830700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1607600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1628400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1593700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1587100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1174400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,217 +2165,232 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>343900</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4287000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3282000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3723000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3890000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4241000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2718000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3121700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2963100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2192700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2044800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2337500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2698000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2112000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2593800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5071000</v>
+      </c>
+      <c r="E44" s="3">
         <v>6205000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7388000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6580000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3895000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3785000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3722900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3799800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3396500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3491700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3488800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3599000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2722500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3300800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1194000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1031000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1758000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>903000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>590000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>660000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>562300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>935100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>967900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1171100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1286200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1509600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1349800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1121600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12841000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12992000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16033000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14337000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11363000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9086000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9103400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9170400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8387800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8315100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8740900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9400300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7771400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8534500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>123000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>115000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>131000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>102800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>128100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>421700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>536100</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L47" s="3" t="s">
         <v>8</v>
@@ -2300,102 +2404,111 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2892000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2870000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2947000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2762000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2739000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2821000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2336200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2239500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2317000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2257600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2092200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2288700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2174600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2076400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1684000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1380000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1454000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1753000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1303000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1327000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1404100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1545600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1347000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1345800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>415200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>377200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>343600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>31400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E52" s="3">
         <v>248000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>694000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>165000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>163200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>164900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>58900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>541500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>466400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>404600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>433900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>302000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>262900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18381000</v>
+      </c>
+      <c r="E54" s="3">
         <v>18257000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21407000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19325000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15836000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13690000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13499400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13715900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12593400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12385000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11652900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12500100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10591600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11033800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5147000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4468000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5724000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6254000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5247000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5108000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5147200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5122300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4484900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4248300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4561200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4747800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3705300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4294900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1209000</v>
+      </c>
+      <c r="E58" s="3">
         <v>137000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>274000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1081000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>395600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>263100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>632600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>43000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>61500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>65200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>419500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>42400</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2934000</v>
+      </c>
+      <c r="E59" s="3">
         <v>3446000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4363000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2906000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1718400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1475900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1426100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1719400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1958200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2258700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3958000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2872100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2048000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1950900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9850000</v>
+      </c>
+      <c r="E60" s="3">
         <v>8539000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10867000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10711000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7834000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7211000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7597500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7268100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6504600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6572200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6755100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7656700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6172800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6288200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2939000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3751000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4048000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3799000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4077000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3218000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2421900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2897600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2890600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2709400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2026000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2074700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1657300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2157800</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>590000</v>
+      </c>
+      <c r="E62" s="3">
         <v>464000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>715000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>522000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>489000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>430000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>507600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>531600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>519900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>497900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>475600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>567100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>514700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>607600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13379000</v>
+      </c>
+      <c r="E66" s="3">
         <v>12932000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15701000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15118000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12400000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10859000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10527000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10697300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9948800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9814100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9292100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10337100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8344800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8749800</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>446000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-560000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1353000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2289000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2902000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-3012000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3144100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3572600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3892200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-4336300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4937100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-5302700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5579700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5002000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5325000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5351000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4129000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3436000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2831000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2972400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3018600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2644500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2570900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2360800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2163100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2246800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2284000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>838000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1006000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>793000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>936000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>613000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>88000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>93000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>428500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>319600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>444100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>600800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>365600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>277100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>488800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>467000</v>
+      </c>
+      <c r="E83" s="3">
         <v>431000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>414000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>409000</v>
-      </c>
-      <c r="G83" s="3">
-        <v>422000</v>
       </c>
       <c r="H83" s="3">
         <v>422000</v>
       </c>
       <c r="I83" s="3">
+        <v>422000</v>
+      </c>
+      <c r="J83" s="3">
         <v>433000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>434400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>609700</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3">
         <v>464500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>566400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>521900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1505000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1326000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>950000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1024000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>144000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1533000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2971000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-3866300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3822100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>794000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>1216500</v>
       </c>
       <c r="N89" s="3">
         <v>1216500</v>
       </c>
       <c r="O89" s="3">
+        <v>1216500</v>
+      </c>
+      <c r="P89" s="3">
         <v>1115400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>804300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-438000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-530000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-635000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-443000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-351000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-462000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-726000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-562000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-525100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-347400</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-609600</v>
       </c>
       <c r="N91" s="3">
         <v>-609600</v>
       </c>
       <c r="O91" s="3">
+        <v>-609600</v>
+      </c>
+      <c r="P91" s="3">
         <v>-489000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-437200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-838000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-492000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-604000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-951000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-202000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2279000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>3253000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3710900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>4269800</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-783900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-697200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-481400</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,8 +4455,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4267,9 +4500,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-821000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1656000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>280000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>743000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-508000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-187800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-242100</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-410800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-339600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-522200</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-26000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>29000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-27000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-15100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>17500</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3">
         <v>-15100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-185000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-820000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>330000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>327000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>714000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>226000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>225000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-358300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>223100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>34700</v>
-      </c>
-      <c r="M102" s="3">
-        <v>6600</v>
       </c>
       <c r="N102" s="3">
         <v>6600</v>
       </c>
       <c r="O102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="P102" s="3">
         <v>68800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-230100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>FLEX</t>
   </si>
@@ -991,7 +991,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>86000</v>
+        <v>67000</v>
       </c>
       <c r="E14" s="3">
         <v>175000</v>
@@ -1220,7 +1220,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-11000</v>
+        <v>8000</v>
       </c>
       <c r="E20" s="3">
         <v>36000</v>
@@ -1268,7 +1268,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1336000</v>
+        <v>1317000</v>
       </c>
       <c r="E21" s="3">
         <v>1062000</v>
@@ -1796,7 +1796,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>11000</v>
+        <v>-8000</v>
       </c>
       <c r="E32" s="3">
         <v>-36000</v>
@@ -2368,8 +2368,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>119000</v>
       </c>
       <c r="E47" s="3">
         <v>123000</v>
@@ -2609,7 +2609,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>964000</v>
+        <v>268000</v>
       </c>
       <c r="E52" s="3">
         <v>248000</v>
@@ -2841,10 +2841,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1209000</v>
+        <v>1344000</v>
       </c>
       <c r="E58" s="3">
-        <v>137000</v>
+        <v>136000</v>
       </c>
       <c r="F58" s="3">
         <v>274000</v>
@@ -2889,10 +2889,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2934000</v>
+        <v>2799000</v>
       </c>
       <c r="E59" s="3">
-        <v>3446000</v>
+        <v>3447000</v>
       </c>
       <c r="F59" s="3">
         <v>4363000</v>
@@ -3036,7 +3036,7 @@
         <v>590000</v>
       </c>
       <c r="E62" s="3">
-        <v>464000</v>
+        <v>642000</v>
       </c>
       <c r="F62" s="3">
         <v>715000</v>
@@ -3484,8 +3484,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>1284000</v>
       </c>
       <c r="E72" s="3">
         <v>446000</v>
@@ -3894,7 +3894,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>467000</v>
+        <v>439000</v>
       </c>
       <c r="E83" s="3">
         <v>431000</v>

--- a/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLEX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>FLEX</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27914000</v>
+      </c>
+      <c r="E8" s="3">
         <v>25813000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26415000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28502000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24633000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24124000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24210000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26211000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>25441100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23862900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>24418900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26147900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26108600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>23569500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>29343000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>25288000</v>
+      </c>
+      <c r="E9" s="3">
         <v>23584000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>24395000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26503000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>22838000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>22349000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>22681000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24594000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23778400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22303200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>22810800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24602600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24609700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>44374800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>27825100</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2626000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2229000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2020000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1999000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1795000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1775000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1529000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1617000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1662700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1559700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1608100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1545300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1498900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-20805300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1518000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>138000</v>
+      </c>
+      <c r="E14" s="3">
         <v>67000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>175000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>27000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>138000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>321200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>219000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-77700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>49400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-8000</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>75300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>227400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-20000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>70000</v>
+        <v>68000</v>
       </c>
       <c r="E15" s="3">
         <v>70000</v>
       </c>
       <c r="F15" s="3">
+        <v>70000</v>
+      </c>
+      <c r="G15" s="3">
         <v>81000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>62000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>64000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>74000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>78600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>81400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>66000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>32000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>28900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>29500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>49600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>26408000</v>
+      </c>
+      <c r="E17" s="3">
         <v>24558000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>25387000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>27458000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>23728000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>23228000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>23579000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>25621000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24876400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>23392600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>23871400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25425900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25646200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23184400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>28768300</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1506000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1255000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1028000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1044000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>905000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>896000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>631000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>590000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>564700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>470400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>547500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>722100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>462400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>385100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>574700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E20" s="3">
         <v>8000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>36000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-226000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-104000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>31000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>62000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>17200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>18000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1513000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1317000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1062000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1115000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1191000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1062000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>664000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>602000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>626100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1088500</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>944900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>964100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1096700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>215000</v>
+      </c>
+      <c r="E22" s="3">
         <v>218000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>207000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>230000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>166000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>162000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>138800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>146000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>123100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>108000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>98000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>76400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>79900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>68900</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1143000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1023000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>666000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>807000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>964000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>714000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>159000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>182000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>520900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>370800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>454700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>670700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>328800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>574700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E24" s="3">
         <v>185000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-206000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>92000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>101000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>71000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>89000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>92400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>51300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>10600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>69900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>34900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>54000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E26" s="3">
         <v>838000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>872000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>683000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>872000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>613000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>88000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>93000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>428500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>319600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>444100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>600800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>365600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>302500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>520800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E27" s="3">
         <v>838000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1006000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>793000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>936000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>613000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>88000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>93000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>428500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>319600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>444100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>600800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>365600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>302500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>520800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1655,17 +1715,17 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>373000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>350000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>68000</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
@@ -1688,14 +1748,17 @@
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-25500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-32000</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-36000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>226000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>104000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-31000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-62000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-17200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-18000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E33" s="3">
         <v>838000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1006000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>793000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>936000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>613000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>88000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>93000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>428500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>319600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>444100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>600800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>365600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>277100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>488800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E35" s="3">
         <v>838000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1006000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>793000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>936000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>613000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>88000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>93000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>428500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>319600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>444100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>600800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>365600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>277100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>488800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,56 +2160,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2389000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2289000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2474000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3164000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2964000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2637000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1923000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1696600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1472400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1830700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1607600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1628400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1593700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1587100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1174400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2168,232 +2257,247 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>343900</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5742000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4287000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3282000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3723000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3890000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4241000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2718000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3121700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2963100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2192700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2044800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2337500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2698000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2112000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2593800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5845000</v>
+      </c>
+      <c r="E44" s="3">
         <v>5071000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6205000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7388000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6580000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3895000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3785000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3722900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3799800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3396500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3491700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3488800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3599000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2722500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3300800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2356000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1194000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1031000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1758000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>903000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>590000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>660000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>562300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>935100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>967900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1171100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1286200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1509600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1349800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1121600</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16332000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12841000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12992000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16033000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14337000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11363000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9086000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9103400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9170400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8387800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8315100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8740900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9400300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7771400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8534500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E47" s="3">
         <v>119000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>123000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>115000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>131000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>102800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>128100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>421700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>536100</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -2407,108 +2511,117 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3164000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2892000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2870000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2947000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2762000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2739000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2821000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2336200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2239500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2317000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2257600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2092200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2288700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2174600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2076400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1652000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1684000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1380000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1454000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1753000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1303000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1327000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1404100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1545600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1347000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1345800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>415200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>377200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>343600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>31400</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>307000</v>
+      </c>
+      <c r="E52" s="3">
         <v>268000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>248000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>694000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>165000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>163200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>164900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>69300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>541500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>466400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>404600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>433900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>302000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>262900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22060000</v>
+      </c>
+      <c r="E54" s="3">
         <v>18381000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18257000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21407000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19325000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15836000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13690000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13499400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13715900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12593400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12385000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11652900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12500100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10591600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11033800</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8055000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5147000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4468000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5724000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>6254000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5247000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5108000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5147200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5122300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4484900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4248300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4561200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4747800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3705300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4294900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1344000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>136000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>274000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1081000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>395600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>263100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>632600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>43000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>61500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>65200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>45000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>36800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>419500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>42400</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3141000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2799000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3447000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4363000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2906000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1718400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1475900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1426100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1719400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1958200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2258700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3958000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2872100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2048000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1950900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>12016000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9850000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8539000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10867000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10711000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7834000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7211000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7597500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7268100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6504600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6572200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6755100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7656700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6172800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6288200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4316000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2939000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3751000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4048000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3799000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4077000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3218000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2421900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2897600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2890600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2709400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2026000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2074700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1657300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2157800</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>584000</v>
+      </c>
+      <c r="E62" s="3">
         <v>590000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>642000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>715000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>522000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>489000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>430000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>507600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>531600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>519900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>497900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>475600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>567100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>514700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>607600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16916000</v>
+      </c>
+      <c r="E66" s="3">
         <v>13379000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12932000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>15701000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15118000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12400000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10859000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10527000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10697300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9948800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9814100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9292100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10337100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8344800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8749800</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2164000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1284000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>446000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-560000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1353000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2289000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-2902000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-3012000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-3144100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-3572600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-3892200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-4336300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-4937100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-5302700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-5579700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5144000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5002000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5325000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5351000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4129000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3436000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2831000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2972400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3018600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2644500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2570900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2360800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2163100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2246800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2284000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>880000</v>
+      </c>
+      <c r="E81" s="3">
         <v>838000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1006000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>793000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>936000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>613000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>88000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>93000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>428500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>319600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>444100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>600800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>365600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>277100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>488800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E83" s="3">
         <v>439000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>431000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>414000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>409000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>422000</v>
       </c>
       <c r="I83" s="3">
         <v>422000</v>
       </c>
       <c r="J83" s="3">
+        <v>422000</v>
+      </c>
+      <c r="K83" s="3">
         <v>433000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>434400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>609700</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>464500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>566400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>521900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1685000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1505000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1326000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>950000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1024000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>144000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1533000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2971000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3866300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3822100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>794000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>1216500</v>
       </c>
       <c r="O89" s="3">
         <v>1216500</v>
       </c>
       <c r="P89" s="3">
+        <v>1216500</v>
+      </c>
+      <c r="Q89" s="3">
         <v>1115400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>804300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-633000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-438000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-530000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-635000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-443000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-351000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-462000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-726000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-562000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-525100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-347400</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-609600</v>
       </c>
       <c r="O91" s="3">
         <v>-609600</v>
       </c>
       <c r="P91" s="3">
+        <v>-609600</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-489000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-437200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-672000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-838000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-492000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-604000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-951000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-202000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2279000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3253000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3710900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>4269800</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>-783900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-697200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-481400</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,8 +4688,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4503,9 +4736,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-924000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-821000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1656000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>280000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>743000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-508000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-30000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-242100</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-410800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-339600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-522200</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-31000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-18000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-26000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>29000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-27000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-15100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>17500</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>-15100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-30900</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-185000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-820000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>330000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>327000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>714000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>226000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>225000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-358300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>223100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34700</v>
-      </c>
-      <c r="N102" s="3">
-        <v>6600</v>
       </c>
       <c r="O102" s="3">
         <v>6600</v>
       </c>
       <c r="P102" s="3">
+        <v>6600</v>
+      </c>
+      <c r="Q102" s="3">
         <v>68800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-230100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
